--- a/Flutter_loc.xlsx
+++ b/Flutter_loc.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/component_test_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACCF1CE-F56A-0E42-BF0C-5B055CE33437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54B61B0-7B7F-4347-8D52-2E663A473D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{C6571707-2328-3E4C-B114-DF4871663406}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" activeTab="1" xr2:uid="{C6571707-2328-3E4C-B114-DF4871663406}"/>
   </bookViews>
   <sheets>
     <sheet name="ems_loc_making" sheetId="3" r:id="rId1"/>
     <sheet name="ems_loc_testing" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="75">
   <si>
     <t>language</t>
   </si>
@@ -1486,6 +1487,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2076,4 +2078,850 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D154569-45A1-254E-8684-FBCB99D7A925}">
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2">
+        <v>27</v>
+      </c>
+      <c r="E2" s="2">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="2">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="2">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>49</v>
+      </c>
+      <c r="F24" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="2">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="2">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="2">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="2">
+        <v>4</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="4">
+        <v>426</v>
+      </c>
+      <c r="E42" s="4">
+        <v>120</v>
+      </c>
+      <c r="F42" s="4">
+        <v>3856</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>